--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484087_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484087_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.8008</v>
+        <v>6.6042</v>
       </c>
       <c r="E2" t="n">
-        <v>5.3271</v>
+        <v>5.8599</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4738</v>
+        <v>0.7443</v>
       </c>
       <c r="G2" t="n">
         <v>5.6687</v>
@@ -610,13 +610,13 @@
         <v>1.9838</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.6225000000000001</v>
+        <v>-0.8191000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.3658</v>
+        <v>-0.833</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7433999999999999</v>
+        <v>0.0139</v>
       </c>
       <c r="V2" t="n">
         <v>2.9449</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.9673</v>
+        <v>2.5644</v>
       </c>
       <c r="E3" t="n">
-        <v>4.6211</v>
+        <v>3.4988</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.6538</v>
+        <v>-0.9343</v>
       </c>
       <c r="G3" t="n">
         <v>-0.572</v>
@@ -688,13 +688,13 @@
         <v>0.5952</v>
       </c>
       <c r="S3" t="n">
-        <v>1.3887</v>
+        <v>-0.0142</v>
       </c>
       <c r="T3" t="n">
-        <v>1.6042</v>
+        <v>0.4818</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2155</v>
+        <v>-0.496</v>
       </c>
       <c r="V3" t="n">
         <v>2.5555</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4088</v>
+        <v>0.2545</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1865</v>
+        <v>0.2286</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2223</v>
+        <v>0.0259</v>
       </c>
       <c r="G4" t="n">
         <v>1.0316</v>
@@ -766,13 +766,13 @@
         <v>1.5871</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8496</v>
+        <v>-0.3047</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8673999999999999</v>
+        <v>-0.0906</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0177</v>
+        <v>-0.2141</v>
       </c>
       <c r="V4" t="n">
         <v>-0.8692</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. CRUZ JOBACHO</t>
+          <t>A. BELTRAN MATA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.6542</v>
+        <v>0.0272</v>
       </c>
       <c r="E5" t="n">
-        <v>2.9111</v>
+        <v>1.3226</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.5653</v>
+        <v>-1.2953</v>
       </c>
       <c r="G5" t="n">
-        <v>2.4472</v>
+        <v>-0.38</v>
       </c>
       <c r="H5" t="n">
-        <v>1.149</v>
+        <v>-1.1897</v>
       </c>
       <c r="I5" t="n">
-        <v>1.2982</v>
+        <v>0.8097</v>
       </c>
       <c r="J5" t="n">
-        <v>2.2933</v>
+        <v>2.2302</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0081</v>
+        <v>-0.5486</v>
       </c>
       <c r="L5" t="n">
-        <v>1.2852</v>
+        <v>2.7788</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1539</v>
+        <v>-2.6102</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1409</v>
+        <v>-0.6411</v>
       </c>
       <c r="O5" t="n">
-        <v>0.013</v>
+        <v>-1.9691</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1984</v>
+        <v>0.7935</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.1903</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1984</v>
+        <v>1.9838</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0176</v>
+        <v>-0.9183</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6178</v>
+        <v>-0.2493</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6354</v>
+        <v>-0.669</v>
       </c>
       <c r="V5" t="n">
-        <v>-3.2821</v>
+        <v>0.532</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.532</v>
       </c>
       <c r="X5" t="n">
-        <v>-3.2821</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. BELTRAN MATA</t>
+          <t>A. DIEZ VALERO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-0.5672</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9540999999999999</v>
+        <v>-0.8672</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.632</v>
+        <v>0.3</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.38</v>
+        <v>-0.4737</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.1897</v>
+        <v>-0.8818</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8097</v>
+        <v>0.4081</v>
       </c>
       <c r="J6" t="n">
-        <v>2.2302</v>
+        <v>-0.6802</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.5486</v>
+        <v>-0.6802</v>
       </c>
       <c r="L6" t="n">
-        <v>2.7788</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.6102</v>
+        <v>0.2065</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6411</v>
+        <v>-0.2016</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.9691</v>
+        <v>0.4081</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7935</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1903</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.9838</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.6234</v>
+        <v>-0.0935</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6177</v>
+        <v>-0.187</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.0057</v>
+        <v>0.0935</v>
       </c>
       <c r="V6" t="n">
-        <v>0.532</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.532</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. DIEZ VALERO</t>
+          <t>L. MARTÍN LLAVERÍA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6857</v>
+        <v>-0.9778</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9296</v>
+        <v>4.0719</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2439</v>
+        <v>-5.0496</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.4737</v>
+        <v>3.5566</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.8818</v>
+        <v>-0.3326</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4081</v>
+        <v>3.8892</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.6802</v>
+        <v>4.1799</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.6802</v>
+        <v>-0.0849</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>4.2648</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2065</v>
+        <v>-0.6233</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2016</v>
+        <v>-0.2477</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4081</v>
+        <v>-0.3756</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.3887</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.3887</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.212</v>
+        <v>-1.3632</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2494</v>
+        <v>-0.374</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0374</v>
+        <v>-0.9892</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-4.5599</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-4.8259</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. GARCIA IBAÑEZ</t>
+          <t>A. CRUZ JOBACHO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.0782</v>
+        <v>-0.9781</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.5308</v>
+        <v>2.503</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4526</v>
+        <v>-3.4811</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.0834</v>
+        <v>2.4472</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.0834</v>
+        <v>1.149</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1.2982</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.3604</v>
+        <v>2.2933</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6802</v>
+        <v>1.0081</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6802</v>
+        <v>1.2852</v>
       </c>
       <c r="M8" t="n">
-        <v>0.277</v>
+        <v>0.1539</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4032</v>
+        <v>0.1409</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6802</v>
+        <v>0.013</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.1984</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>0.1984</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2607</v>
+        <v>-0.3415</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4364</v>
+        <v>0.2097</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1757</v>
+        <v>-0.5513</v>
       </c>
       <c r="V8" t="n">
-        <v>0.266</v>
+        <v>-3.2821</v>
       </c>
       <c r="W8" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-3.2821</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>L. MARTÍN LLAVERÍA</t>
+          <t>M. GARCIA IBAÑEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.8206</v>
+        <v>-1.0158</v>
       </c>
       <c r="E9" t="n">
-        <v>3.3973</v>
+        <v>-1.4685</v>
       </c>
       <c r="F9" t="n">
-        <v>-5.218</v>
+        <v>0.4526</v>
       </c>
       <c r="G9" t="n">
-        <v>3.5566</v>
+        <v>-1.0834</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.3326</v>
+        <v>-1.0834</v>
       </c>
       <c r="I9" t="n">
-        <v>3.8892</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>4.1799</v>
+        <v>-1.3604</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.0849</v>
+        <v>-0.6802</v>
       </c>
       <c r="L9" t="n">
-        <v>4.2648</v>
+        <v>-0.6802</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.6233</v>
+        <v>0.277</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2477</v>
+        <v>-0.4032</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.3756</v>
+        <v>0.6802</v>
       </c>
       <c r="P9" t="n">
-        <v>1.3887</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3887</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.206</v>
+        <v>-0.1984</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.0485</v>
+        <v>-0.3741</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.1575</v>
+        <v>0.1757</v>
       </c>
       <c r="V9" t="n">
-        <v>-4.5599</v>
+        <v>0.266</v>
       </c>
       <c r="W9" t="n">
         <v>0.266</v>
       </c>
       <c r="X9" t="n">
-        <v>-4.8259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.2898</v>
+        <v>-1.4827</v>
       </c>
       <c r="E10" t="n">
-        <v>1.5081</v>
+        <v>1.9786</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.7979</v>
+        <v>-3.4613</v>
       </c>
       <c r="G10" t="n">
         <v>3.9501</v>
@@ -1234,13 +1234,13 @@
         <v>1.9838</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.1562</v>
+        <v>-1.349</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.1165</v>
+        <v>-0.646</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.0397</v>
+        <v>-0.703</v>
       </c>
       <c r="V10" t="n">
         <v>-3.8854</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.839</v>
+        <v>-2.4323</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.3116</v>
+        <v>-1.0452</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.5275</v>
+        <v>-1.3872</v>
       </c>
       <c r="G11" t="n">
         <v>0.0707</v>
@@ -1312,13 +1312,13 @@
         <v>0.1984</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9098000000000001</v>
+        <v>-0.5031</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5611</v>
+        <v>-0.2947</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3486</v>
+        <v>-0.2084</v>
       </c>
       <c r="V11" t="n">
         <v>-1.2065</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.0344</v>
+        <v>-6.2758</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.213</v>
+        <v>-6.5385</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1785</v>
+        <v>0.2627</v>
       </c>
       <c r="G12" t="n">
         <v>-2.4139</v>
@@ -1390,13 +1390,13 @@
         <v>0.9919</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.7124</v>
+        <v>-0.9537</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.4339</v>
+        <v>-0.7594</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2785</v>
+        <v>-0.1943</v>
       </c>
       <c r="V12" t="n">
         <v>0.266</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.902899999999999</v>
+        <v>-4.279399999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>8.920300000000001</v>
+        <v>9.543999999999997</v>
       </c>
       <c r="F13" t="n">
-        <v>-13.8234</v>
+        <v>-13.8233</v>
       </c>
       <c r="G13" t="n">
         <v>11.8019</v>
@@ -1441,7 +1441,7 @@
         <v>17.5225</v>
       </c>
       <c r="J13" t="n">
-        <v>19.01029999999999</v>
+        <v>19.0103</v>
       </c>
       <c r="K13" t="n">
         <v>-0.8755000000000002</v>
@@ -1468,13 +1468,13 @@
         <v>10.9111</v>
       </c>
       <c r="S13" t="n">
-        <v>-7.482299999999999</v>
+        <v>-6.858700000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.7399</v>
+        <v>-3.1166</v>
       </c>
       <c r="U13" t="n">
-        <v>-3.742100000000001</v>
+        <v>-3.7422</v>
       </c>
       <c r="V13" t="n">
         <v>-7.2387</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.2386</v>
+        <v>4.8238</v>
       </c>
       <c r="E14" t="n">
-        <v>9.050000000000001</v>
+        <v>7.7236</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.8114</v>
+        <v>-2.8998</v>
       </c>
       <c r="G14" t="n">
         <v>-0.522</v>
@@ -1546,13 +1546,13 @@
         <v>1.3887</v>
       </c>
       <c r="S14" t="n">
-        <v>3.2683</v>
+        <v>1.8535</v>
       </c>
       <c r="T14" t="n">
-        <v>2.4375</v>
+        <v>1.1111</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8308</v>
+        <v>0.7423999999999999</v>
       </c>
       <c r="V14" t="n">
         <v>3.6907</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.1803</v>
+        <v>4.0196</v>
       </c>
       <c r="E15" t="n">
-        <v>5.4873</v>
+        <v>5.6913</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.307</v>
+        <v>-1.6717</v>
       </c>
       <c r="G15" t="n">
         <v>2.8189</v>
@@ -1624,13 +1624,13 @@
         <v>0.9919</v>
       </c>
       <c r="S15" t="n">
-        <v>1.5083</v>
+        <v>1.3476</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6973</v>
+        <v>0.9013</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.4463</v>
       </c>
       <c r="V15" t="n">
         <v>-0.9405</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. TUGORES SOTO</t>
+          <t>M. MAÑES CARRETERO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.7529</v>
+        <v>2.1899</v>
       </c>
       <c r="E16" t="n">
-        <v>4.2015</v>
+        <v>5.4034</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.4486</v>
+        <v>-3.2135</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6923</v>
+        <v>-3.5503</v>
       </c>
       <c r="H16" t="n">
-        <v>2.1367</v>
+        <v>1.6127</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.4444</v>
+        <v>-5.163</v>
       </c>
       <c r="J16" t="n">
-        <v>5.1203</v>
+        <v>0.068</v>
       </c>
       <c r="K16" t="n">
-        <v>2.309</v>
+        <v>1.649</v>
       </c>
       <c r="L16" t="n">
-        <v>2.8113</v>
+        <v>-1.5809</v>
       </c>
       <c r="M16" t="n">
-        <v>-4.428</v>
+        <v>-3.6183</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1723</v>
+        <v>-0.0363</v>
       </c>
       <c r="O16" t="n">
-        <v>-4.2557</v>
+        <v>-3.582</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.7855</v>
+        <v>1.3887</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.5709</v>
+        <v>-0.5952</v>
       </c>
       <c r="R16" t="n">
-        <v>1.7855</v>
+        <v>1.9838</v>
       </c>
       <c r="S16" t="n">
-        <v>2.5683</v>
+        <v>1.9385</v>
       </c>
       <c r="T16" t="n">
-        <v>1.4456</v>
+        <v>0.5727</v>
       </c>
       <c r="U16" t="n">
-        <v>1.1227</v>
+        <v>1.3658</v>
       </c>
       <c r="V16" t="n">
-        <v>1.2777</v>
+        <v>2.4129</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2065</v>
+        <v>5.3578</v>
       </c>
       <c r="X16" t="n">
-        <v>0.0713</v>
+        <v>-2.9449</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. MAÑES CARRETERO</t>
+          <t>D. TUGORES SOTO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.8905</v>
+        <v>2.0905</v>
       </c>
       <c r="E17" t="n">
-        <v>4.7912</v>
+        <v>3.4873</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.9007</v>
+        <v>-1.3967</v>
       </c>
       <c r="G17" t="n">
-        <v>-3.5503</v>
+        <v>0.6923</v>
       </c>
       <c r="H17" t="n">
-        <v>1.6127</v>
+        <v>2.1367</v>
       </c>
       <c r="I17" t="n">
-        <v>-5.163</v>
+        <v>-1.4444</v>
       </c>
       <c r="J17" t="n">
-        <v>0.068</v>
+        <v>5.1203</v>
       </c>
       <c r="K17" t="n">
-        <v>1.649</v>
+        <v>2.309</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.5809</v>
+        <v>2.8113</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.6183</v>
+        <v>-4.428</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0363</v>
+        <v>-0.1723</v>
       </c>
       <c r="O17" t="n">
-        <v>-3.582</v>
+        <v>-4.2557</v>
       </c>
       <c r="P17" t="n">
-        <v>1.3887</v>
+        <v>-1.7855</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.5952</v>
+        <v>-3.5709</v>
       </c>
       <c r="R17" t="n">
-        <v>1.9838</v>
+        <v>1.7855</v>
       </c>
       <c r="S17" t="n">
-        <v>1.6392</v>
+        <v>1.9059</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0395</v>
+        <v>0.7314000000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>1.6787</v>
+        <v>1.1746</v>
       </c>
       <c r="V17" t="n">
-        <v>2.4129</v>
+        <v>1.2777</v>
       </c>
       <c r="W17" t="n">
-        <v>5.3578</v>
+        <v>1.2065</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.9449</v>
+        <v>0.0713</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>,. VICENTE SABARIEGO</t>
+          <t>P. MULIO CAMPOS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2048</v>
+        <v>0.1911</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.08459999999999999</v>
+        <v>-1.7825</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2895</v>
+        <v>1.9736</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.1333</v>
+        <v>-0.5217000000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.1333</v>
+        <v>-0.0709</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>-0.4508</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.1333</v>
+        <v>-1.1591</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.1333</v>
+        <v>-0.5592</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-0.5999</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>0.6374</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>0.4883</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>0.149</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.9919</v>
+        <v>1.1903</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.1903</v>
       </c>
       <c r="S18" t="n">
-        <v>2.2588</v>
+        <v>0.197</v>
       </c>
       <c r="T18" t="n">
-        <v>2.0406</v>
+        <v>0.0511</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2182</v>
+        <v>0.1459</v>
       </c>
       <c r="V18" t="n">
-        <v>0.0713</v>
+        <v>-0.6745</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>-0.6745</v>
       </c>
       <c r="X18" t="n">
-        <v>0.0713</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. MULIO CAMPOS</t>
+          <t>A. CRUZ URBANEJA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6073</v>
+        <v>0.0589</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.4967</v>
+        <v>1.5862</v>
       </c>
       <c r="F19" t="n">
-        <v>1.8894</v>
+        <v>-1.5273</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.5217000000000001</v>
+        <v>-3.3157</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.0709</v>
+        <v>-1.0276</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4508</v>
+        <v>-2.2881</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.1591</v>
+        <v>-0.4843</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.5592</v>
+        <v>-0.9816</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5999</v>
+        <v>0.4973</v>
       </c>
       <c r="M19" t="n">
-        <v>0.6374</v>
+        <v>-2.8313</v>
       </c>
       <c r="N19" t="n">
-        <v>0.4883</v>
+        <v>-0.046</v>
       </c>
       <c r="O19" t="n">
-        <v>0.149</v>
+        <v>-2.7853</v>
       </c>
       <c r="P19" t="n">
-        <v>1.1903</v>
+        <v>0.9919</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.5952</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1903</v>
+        <v>1.5871</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6014</v>
+        <v>0.8389</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6631</v>
+        <v>0.856</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0617</v>
+        <v>-0.0171</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.6745</v>
+        <v>1.5437</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.6745</v>
+        <v>1.8097</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.9064</v>
+        <v>-0.0979</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.2326</v>
+        <v>0.3796</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6738</v>
+        <v>-0.4775</v>
       </c>
       <c r="G20" t="n">
         <v>-0.6009</v>
@@ -2010,13 +2010,13 @@
         <v>0.7935</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.099</v>
+        <v>-0.2905</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4137</v>
+        <v>0.1985</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6853</v>
+        <v>-0.4889</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2043,13 +2043,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.9064</v>
+        <v>-0.0979</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.2326</v>
+        <v>0.3796</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.6738</v>
+        <v>-0.4775</v>
       </c>
       <c r="G21" t="n">
         <v>-0.6009</v>
@@ -2088,13 +2088,13 @@
         <v>0.7935</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.099</v>
+        <v>-0.2905</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4137</v>
+        <v>0.1985</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6853</v>
+        <v>-0.4889</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2109,7 +2109,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. CRUZ URBANEJA</t>
+          <t>,. VICENTE SABARIEGO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2121,67 +2121,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.3184</v>
+        <v>-1.113</v>
       </c>
       <c r="E22" t="n">
-        <v>0.77</v>
+        <v>-1.309</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.0885</v>
+        <v>0.196</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.3157</v>
+        <v>-1.1333</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.0276</v>
+        <v>-1.1333</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.2881</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.4843</v>
+        <v>-1.1333</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.9816</v>
+        <v>-1.1333</v>
       </c>
       <c r="L22" t="n">
-        <v>0.4973</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.8313</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.046</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>-2.7853</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>0.9919</v>
+        <v>-0.9919</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.5952</v>
+        <v>-0.9919</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5871</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5384</v>
+        <v>0.9409</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0398</v>
+        <v>0.8162</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5782</v>
+        <v>0.1247</v>
       </c>
       <c r="V22" t="n">
-        <v>1.5437</v>
+        <v>0.0713</v>
       </c>
       <c r="W22" t="n">
-        <v>1.8097</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.266</v>
+        <v>0.0713</v>
       </c>
     </row>
     <row r="23">
@@ -2199,13 +2199,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.7228</v>
+        <v>-1.3904</v>
       </c>
       <c r="E23" t="n">
         <v>-1.5442</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.1786</v>
+        <v>0.1538</v>
       </c>
       <c r="G23" t="n">
         <v>-0.5548999999999999</v>
@@ -2244,13 +2244,13 @@
         <v>1.5871</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6286</v>
+        <v>-0.2961</v>
       </c>
       <c r="T23" t="n">
         <v>-0.5554</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0732</v>
+        <v>0.2592</v>
       </c>
       <c r="V23" t="n">
         <v>-0.1425</v>
@@ -2277,13 +2277,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.8093</v>
+        <v>-4.8367</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.1186</v>
+        <v>-5.5065</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3093</v>
+        <v>0.6698</v>
       </c>
       <c r="G24" t="n">
         <v>-5.1144</v>
@@ -2322,13 +2322,13 @@
         <v>1.5871</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.8933</v>
+        <v>0.0794</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.2469</v>
+        <v>-0.6347</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3536</v>
+        <v>0.7141</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2355,13 +2355,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>3.996500000000001</v>
+        <v>5.837899999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>13.5907</v>
+        <v>14.5088</v>
       </c>
       <c r="F25" t="n">
-        <v>-9.594199999999999</v>
+        <v>-8.670799999999998</v>
       </c>
       <c r="G25" t="n">
         <v>-12.4029</v>
@@ -2373,7 +2373,7 @@
         <v>-17.9668</v>
       </c>
       <c r="J25" t="n">
-        <v>7.3893</v>
+        <v>7.389299999999999</v>
       </c>
       <c r="K25" t="n">
         <v>4.9458</v>
@@ -2391,7 +2391,7 @@
         <v>-20.4106</v>
       </c>
       <c r="P25" t="n">
-        <v>2.7772</v>
+        <v>2.777199999999999</v>
       </c>
       <c r="Q25" t="n">
         <v>-10.9112</v>
@@ -2400,13 +2400,13 @@
         <v>13.6885</v>
       </c>
       <c r="S25" t="n">
-        <v>6.3832</v>
+        <v>8.224600000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>3.3285</v>
+        <v>4.246700000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>3.0547</v>
+        <v>3.9781</v>
       </c>
       <c r="V25" t="n">
         <v>7.238799999999999</v>
